--- a/out/Attention-S4_repeat_5_000001.xlsx
+++ b/out/Attention-S4_repeat_5_000001.xlsx
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>3.415552302146114</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.3291019071641193</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.3291019071641193</v>
       </c>
       <c r="JC43" t="n">
-        <v>-7.549743061384651e-05</v>
+        <v>-7.312052609864622e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.03250700163653785</v>
+        <v>0.03148357556307684</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.06510075586587261</v>
+        <v>0.06305117246534536</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1255909113784595</v>
+        <v>0.121637702591773</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.2838603620831945</v>
+        <v>0.2749235136491289</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.03863297737825833</v>
+        <v>0.03741643918312753</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2353747611161221</v>
+        <v>0.2279647063566104</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.00783871192263551</v>
+        <v>0.007592073838003202</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2123591837899089</v>
+        <v>0.2056738804011557</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.006787130236714228</v>
+        <v>0.006573063941702364</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2180879121040965</v>
+        <v>0.211221909421745</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.003315884100197597</v>
+        <v>0.003210881441042951</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.217924827968996</v>
+        <v>0.2110638077888621</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.001579903061546279</v>
+        <v>0.001529790190713239</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2177652469128931</v>
+        <v>0.2109090825293292</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0006552583008062353</v>
+        <v>0.0006346600232937304</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.2174940408466905</v>
+        <v>0.2106461813741298</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0004526011935854903</v>
+        <v>0.000437939435274994</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.217743387102616</v>
+        <v>0.2108875934754698</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0001857089590046543</v>
+        <v>0.0001799103757916749</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.2176623513565788</v>
+        <v>0.2108088657492867</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>9.388939844386562e-05</v>
+        <v>9.121671199943683e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2176642463538488</v>
+        <v>0.2108105511283004</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>3.383994239731721e-05</v>
+        <v>3.279021422441674e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.2176377769955543</v>
+        <v>0.2107848016248036</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>1.618743066942789e-05</v>
+        <v>1.5614797408092e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.2176363164230874</v>
+        <v>0.2107831988581759</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>5.728762911577315e-06</v>
+        <v>5.164091179389035e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.2176309892779815</v>
+        <v>0.2107778889312337</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.2176253723353827</v>
+        <v>0.210772303873013</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-2.694140733653212e-06</v>
+        <v>-3.155312586922569e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.2176196491787541</v>
+        <v>0.2107666536078597</v>
       </c>
     </row>
     <row r="60">
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.2176144078574532</v>
+        <v>0.2107614122865589</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2176091199186027</v>
+        <v>0.2107561243477084</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2176038480845517</v>
+        <v>0.2107508525136574</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.217603887940024</v>
+        <v>0.2107508923691297</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2176039277954963</v>
+        <v>0.210750932224602</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2176039198244019</v>
+        <v>0.2107509242535075</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.217604079246291</v>
+        <v>0.2107510836753966</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>3.415552302146114</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2176039835931575</v>
+        <v>0.2107509880222632</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>3.415552302146114</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2176043343213138</v>
+        <v>0.2107513387504194</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>3.415552302146114</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2176040872173854</v>
+        <v>0.2107510916464911</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>3.415552302146114</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2176040473619131</v>
+        <v>0.2107510517910188</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>3.415552302146114</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2176039835931575</v>
+        <v>0.2107509880222632</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>3.415552302146114</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2176040553330076</v>
+        <v>0.2107510597621133</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.3291019071641193</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2176039835931575</v>
+        <v>0.2107509880222632</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2176040872173854</v>
+        <v>0.2107510916464911</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2176041828705191</v>
+        <v>0.2107511872996248</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2176041191017632</v>
+        <v>0.2107511235308689</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>2.815552302146114</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.217604079246291</v>
+        <v>0.2107510836753966</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>3.415552302146114</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2176040553330076</v>
+        <v>0.2107510597621133</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.3291019071641193</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2176038082290795</v>
+        <v>0.2107508126581851</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2176037285181347</v>
+        <v>0.2107507329472403</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2176037763447014</v>
+        <v>0.2107507807738071</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2176038959111185</v>
+        <v>0.2107509003402241</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2176038799689296</v>
+        <v>0.2107508843980352</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2176038959111185</v>
+        <v>0.2107509003402241</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2176038799689296</v>
+        <v>0.2107508843980352</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2176039357665908</v>
+        <v>0.2107509401956964</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2176039357665908</v>
+        <v>0.2107509401956964</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>3.415552302146114</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2176039357665908</v>
+        <v>0.2107509401956964</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>3.415552302146114</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2176040872173854</v>
+        <v>0.2107510916464911</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>3.415552302146114</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.217604302436936</v>
+        <v>0.2107513068660416</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.3291019071641193</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2176042147548969</v>
+        <v>0.2107512191840026</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>3.415552302146114</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2176041669283302</v>
+        <v>0.2107511713574359</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>3.415552302146114</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2176042147548969</v>
+        <v>0.2107512191840026</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.3291019071641193</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2176040314197242</v>
+        <v>0.2107510358488299</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2176040393908187</v>
+        <v>0.2107510438199243</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2176040473619131</v>
+        <v>0.2107510517910188</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2176040553330076</v>
+        <v>0.2107510597621133</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2176040553330076</v>
+        <v>0.2107510597621133</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>2.815552302146114</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2176040951884799</v>
+        <v>0.2107510996175855</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>3.415552302146114</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2176041589572358</v>
+        <v>0.2107511633863414</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>3.415552302146114</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2176042705525581</v>
+        <v>0.2107512749816638</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.3291019071641193</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2176043183791249</v>
+        <v>0.2107513228082305</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>3.415552302146114</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2176042785236526</v>
+        <v>0.2107512829527582</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>3.415552302146114</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2176042067838025</v>
+        <v>0.2107512112129082</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>3.415552302146114</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2176043263502193</v>
+        <v>0.210751330779325</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>3.415552302146114</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2176041669283302</v>
+        <v>0.2107511713574359</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2176039357665908</v>
+        <v>0.2107509401956964</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.217603887940024</v>
+        <v>0.2107508923691297</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2176039198244019</v>
+        <v>0.2107509242535075</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2176039835931575</v>
+        <v>0.2107509880222632</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2176039835931575</v>
+        <v>0.2107509880222632</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2176039038822129</v>
+        <v>0.2107509083113186</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2176037843157959</v>
+        <v>0.2107507887449016</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2176037444603236</v>
+        <v>0.2107507488894293</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.217603887940024</v>
+        <v>0.2107508923691297</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2176040234486298</v>
+        <v>0.2107510278777354</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2176040075064408</v>
+        <v>0.2107510119355465</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2176039835931575</v>
+        <v>0.2107509880222632</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2176039437376852</v>
+        <v>0.2107509481667909</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2176038401134573</v>
+        <v>0.210750844542563</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2176037205470402</v>
+        <v>0.2107507249761459</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2176038401134573</v>
+        <v>0.210750844542563</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.217603887940024</v>
+        <v>0.2107508923691297</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2176039835931575</v>
+        <v>0.2107509880222632</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2176038640267406</v>
+        <v>0.2107508684558463</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.9291019071641193</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2176038719978351</v>
+        <v>0.2107508764269408</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_5_000001.xlsx
+++ b/out/Attention-S4_repeat_5_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
-        <v>-7.549743061384651e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.03250700163653785</v>
+        <v>0</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.06510075586587261</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1255909113784595</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.2838603620831945</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.03863297737825833</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2353747611161221</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.00783871192263551</v>
+        <v>0</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2123591837899089</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.006787130236714228</v>
+        <v>0</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2180879121040965</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.003315884100197597</v>
+        <v>0</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.217924827968996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.001579903061546279</v>
+        <v>0</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2177652469128931</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0006552583008062353</v>
+        <v>0</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.2174940408466905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0004526011935854903</v>
+        <v>0</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.217743387102616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0001857089590046543</v>
+        <v>0</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.2176623513565788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>9.388939844386562e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2176642463538488</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>3.383994239731721e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.2176377769955543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>1.618743066942789e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.2176363164230874</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>5.728762911577315e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.2176309892779815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-2.045694596194254e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.2176253723353827</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-2.694140733653212e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.2176196491787541</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-4.173194643232597e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.2176144078574532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.68213567138761e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2176091199186027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.817481666896968e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2176038480845517</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -51022,17 +51022,17 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.217603887940024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -51817,17 +51817,17 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2176039277954963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2176039198244019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.217604079246291</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2176039835931575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2176043343213138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2176040872173854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2176040473619131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2176039835931575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2176040553330076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2176039835931575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2176040872173854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2176041828705191</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2176041191017632</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.217604079246291</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2176040553330076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2176038082290795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2176037285181347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2176037763447014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2176038959111185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2176038799689296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2176038959111185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2176038799689296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2176039357665908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2176039357665908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2176039357665908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2176040872173854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.217604302436936</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2176042147548969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2176041669283302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2176042147548969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2176040314197242</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2176040393908187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2176040473619131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2176040553330076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2176040553330076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2176040951884799</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2176041589572358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2176042705525581</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2176043183791249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2176042785236526</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2176042067838025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2176043263502193</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2176041669283302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2176039357665908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.217603887940024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2176039198244019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2176039835931575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2176039835931575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2176039038822129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2176037843157959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2176037444603236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.217603887940024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2176040234486298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2176040075064408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2176039835931575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2176039437376852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2176038401134573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2176037205470402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2176038401134573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.217603887940024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2176039835931575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2176038640267406</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-4.79359707945414e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell (Force)</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2176038719978351</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_5_000001.xlsx
+++ b/out/Attention-S4_repeat_5_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.01411741226911545</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.01320096105337143</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.51</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.01059143245220184</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.01123016327619553</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.01106937229633331</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.01098214089870453</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.01014859229326248</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.01012732088565826</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.01090594381093979</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.0104839950799942</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.01080825924873352</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.0109543651342392</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.01133953779935837</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.01151459664106369</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.01174601912498474</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.01139029860496521</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.01179134845733643</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.0132693350315094</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.01389676705002785</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.01364225149154663</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.01382046192884445</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.0140533372759819</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.01360346004366875</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.01433300599455833</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.01314369589090347</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.01360037177801132</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.01309806481003761</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.01318817958235741</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.01323352009057999</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.01294908672571182</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.0107148140668869</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.01035929471254349</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.01108784228563309</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.01028832048177719</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.01045116037130356</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.01010686904191971</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.01047033816576004</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.01102514564990997</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.01243411004543304</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.01316646113991737</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01831677928566933</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.02068163454532623</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>-0.0001816752822221024</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.07822410178061202</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.03286951780319214</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>0.1566569630070983</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.3022210742498265</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.02451302111148834</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>0.6830750487817598</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>0.09296489660347235</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.01969492435455322</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>0.5664011813620098</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0</v>
+        <v>0.01886306248949166</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.0239294171333313</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>0.5110173888417329</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0</v>
+        <v>0.01633660823303623</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.0179714635014534</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>0.5248062758631562</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.007985702361668543</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.02695796638727188</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>0.524420894243811</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.003808255384588791</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.02174970507621765</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>0.5240439424238605</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.001583850919478074</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.01935569941997528</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>0.5233983419913631</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.001096175216267276</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.009950332343578339</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>0.5240054028804111</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>0.0004543766478726977</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.01747313886880875</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0</v>
+        <v>0.5238174288811471</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.0002335372651652704</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.01144720613956451</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0</v>
+        <v>0.5238290030499527</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0</v>
+        <v>8.842580738814138e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.01136525720357895</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0</v>
+        <v>0.5237725621866074</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0</v>
+        <v>4.596436025889411e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.01304348558187485</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0</v>
+        <v>0.5237760087290115</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0</v>
+        <v>2.041022794847258e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.01337246224284172</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0</v>
+        <v>0.5237702339116556</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0</v>
+        <v>6.722163543152517e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.01432974636554718</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0</v>
+        <v>0.5237637718849604</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0</v>
+        <v>7.289038596293463e-08</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.01258394122123718</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0</v>
+        <v>0.5237571092005268</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>-2.519583929697793e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.01287607103586197</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0</v>
+        <v>0.5237515287163241</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.0113496333360672</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0</v>
+        <v>0.5237459518591734</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.009938657283782959</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0</v>
+        <v>0.5237405445165164</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-4.777674021158921e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.00832580029964447</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="64">
@@ -51817,17 +51817,17 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.007821172475814819</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0</v>
+        <v>0.5237356632182673</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.009311497211456299</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.009096771478652954</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.01908363774418831</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.01346270740032196</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0</v>
+        <v>0.5237360697440847</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.01269152015447617</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.01295389607548714</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.008195959031581879</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.009676277637481689</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.009901784360408783</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC73" t="n">
-        <v>0</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.03280724212527275</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.01503204181790352</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0</v>
+        <v>0.52373591829329</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.01462750136852264</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0</v>
+        <v>0.5237358545245342</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.01049505919218063</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.01571660116314888</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>0</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.01153019815683365</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC79" t="n">
-        <v>0</v>
+        <v>0.5237355436518504</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.0136958621442318</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0</v>
+        <v>0.5237354639409056</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.01101276278495789</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0</v>
+        <v>0.5237355117674724</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.008961275219917297</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.01441004499793053</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.008806966245174408</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.01048564165830612</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.01033689081668854</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.01233319193124771</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.01270915567874908</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC88" t="n">
-        <v>0</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.01099748164415359</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC89" t="n">
-        <v>0</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.01223073899745941</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0</v>
+        <v>0.5237360378597069</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.0111992359161377</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.01172898709774017</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.01193466782569885</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.01167769730091095</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0</v>
+        <v>0.5237357668424952</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.01162482053041458</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0</v>
+        <v>0.5237357748135897</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.01108358800411224</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.0111406072974205</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.01092155277729034</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.01121173053979874</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0</v>
+        <v>0.5237358306112508</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.01034385710954666</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0</v>
+        <v>0.5237358943800067</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.01112467795610428</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0</v>
+        <v>0.5237360059753291</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.01061389595270157</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0</v>
+        <v>0.5237360538018958</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.01070385426282883</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0</v>
+        <v>0.5237360139464236</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.01110449433326721</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0</v>
+        <v>0.5237359422065735</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.01106758415699005</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0</v>
+        <v>0.5237360617729903</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.01168645918369293</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.009274743497371674</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.009270012378692627</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.007752612233161926</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.006892532110214233</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.006494514644145966</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.007958352565765381</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0</v>
+        <v>0.5237356393049839</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.007574789226055145</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0</v>
+        <v>0.5237355197385668</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.003225319087505341</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0</v>
+        <v>0.5237354798830945</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.003700360655784607</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.00163867324590683</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0</v>
+        <v>0.5237357588714008</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.004081442952156067</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0</v>
+        <v>0.5237357429292118</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.005371533334255219</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.006645597517490387</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0</v>
+        <v>0.5237356791604562</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.00813167542219162</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.008689559996128082</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC121" t="n">
-        <v>0</v>
+        <v>0.5237354559698112</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.008521765470504761</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.009471103549003601</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.009681127965450287</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
+        <v>0.01022553443908691</v>
+      </c>
+      <c r="JB125" t="n">
         <v>1</v>
       </c>
-      <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
-      </c>
       <c r="JC125" t="n">
-        <v>0</v>
+        <v>0.5237355994495116</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-4.79359707945414e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.009509086608886719</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="JC126" t="n">
-        <v>0</v>
+        <v>0.5237356074206061</v>
       </c>
     </row>
   </sheetData>
